--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>URL</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Дата_парсінгу</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +494,11 @@
           <t>https://lnzweb.com/product-absolut-ks</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +536,11 @@
           <t>https://lnzweb.com/product-bast-on</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -563,6 +578,11 @@
           <t>https://lnzweb.com/product-dikvalan</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -600,6 +620,11 @@
           <t>https://lnzweb.com/product-macho</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -637,6 +662,11 @@
           <t>https://lnzweb.com/product-napalm</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -674,6 +704,11 @@
           <t>https://lnzweb.com/product-oktant-vg___</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -711,6 +746,11 @@
           <t>https://lnzweb.com/product-bombardir__</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -748,6 +788,11 @@
           <t>https://lnzweb.com/product-dikvalan-maks</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -785,6 +830,11 @@
           <t>https://lnzweb.com/product-napalm-forte</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -822,6 +872,11 @@
           <t>https://lnzweb.com/product-paracels</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -859,6 +914,11 @@
           <t>https://lnzweb.com/product-syper-macho</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -896,6 +956,11 @@
           <t>https://lnzweb.com/product-fyks-ya-tn</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -933,6 +998,11 @@
           <t>https://lnzweb.com/product-alfa-syper</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -970,6 +1040,11 @@
           <t>https://lnzweb.com/product-dot</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1007,6 +1082,11 @@
           <t>https://lnzweb.com/product-napalm-syper-rayndap-ekstra</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1044,6 +1124,11 @@
           <t>https://lnzweb.com/product-paiot</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1081,6 +1166,11 @@
           <t>https://lnzweb.com/product-altron-ks</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1118,6 +1208,11 @@
           <t>https://lnzweb.com/product-l-teron</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1155,6 +1250,11 @@
           <t>https://lnzweb.com/product-sigma</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1192,6 +1292,11 @@
           <t>https://lnzweb.com/product-cirkyl-ke</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1229,6 +1334,11 @@
           <t>https://lnzweb.com/product-sahara</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1266,6 +1376,11 @@
           <t>https://lnzweb.com/product-oktant-tyrbo</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1303,6 +1418,11 @@
           <t>https://lnzweb.com/product-sahara-syper</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1340,6 +1460,11 @@
           <t>https://lnzweb.com/product-tv-ks_</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1377,6 +1502,11 @@
           <t>https://lnzweb.com/product-sherif-maks</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1414,6 +1544,11 @@
           <t>https://lnzweb.com/product-primys_</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1451,6 +1586,11 @@
           <t>https://lnzweb.com/product-absolut</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1488,6 +1628,11 @@
           <t>https://lnzweb.com/product-ailar-ks</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1525,6 +1670,11 @@
           <t>https://lnzweb.com/product-aksakal____</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1562,6 +1712,11 @@
           <t>https://lnzweb.com/product-ares-tn</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1599,6 +1754,11 @@
           <t>https://lnzweb.com/product-at-k-maks</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1632,6 +1792,11 @@
           <t>https://lnzweb.com/product-at-k-vp_</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1669,6 +1834,11 @@
           <t>https://lnzweb.com/product-at-k-vp______</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1706,6 +1876,11 @@
           <t>https://lnzweb.com/product-banten-rk</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1743,6 +1918,11 @@
           <t>https://lnzweb.com/product-betagard</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1780,6 +1960,11 @@
           <t>https://lnzweb.com/product-bleid</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1817,6 +2002,11 @@
           <t>https://lnzweb.com/product-bombardir-akva_</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1854,6 +2044,11 @@
           <t>https://lnzweb.com/product-bombardir-dyo</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1891,6 +2086,11 @@
           <t>https://lnzweb.com/product-broks-rk_</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1928,6 +2128,11 @@
           <t>https://lnzweb.com/product-velas</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1965,6 +2170,11 @@
           <t>https://lnzweb.com/product-verteks_</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2002,6 +2212,11 @@
           <t>https://lnzweb.com/product-dabl-trai</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2039,6 +2254,11 @@
           <t>https://lnzweb.com/product-dikamba-forte</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2076,6 +2296,11 @@
           <t>https://lnzweb.com/product-ef-mer_</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2113,6 +2338,11 @@
           <t>https://lnzweb.com/product-mpreza</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2150,6 +2380,11 @@
           <t>https://lnzweb.com/product-kairos</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2187,6 +2422,11 @@
           <t>https://lnzweb.com/product-kamzol-tyrbo</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2224,6 +2464,11 @@
           <t>https://lnzweb.com/product-kamzol-rk</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2261,6 +2506,11 @@
           <t>https://lnzweb.com/product-kentavr____</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2298,6 +2548,11 @@
           <t>https://lnzweb.com/product-klatter-ke</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2335,6 +2590,11 @@
           <t>https://lnzweb.com/product-kyshon-ks__</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2372,6 +2632,11 @@
           <t>https://lnzweb.com/product-latina-tn</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2409,6 +2674,11 @@
           <t>https://lnzweb.com/product-matar-ks</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2446,6 +2716,11 @@
           <t>https://lnzweb.com/product-metaksa</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2483,6 +2758,11 @@
           <t>https://lnzweb.com/product-mecenat_</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2520,6 +2800,11 @@
           <t>https://lnzweb.com/product-mirald-ks__</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2557,6 +2842,11 @@
           <t>https://lnzweb.com/product-mysson</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2594,6 +2884,11 @@
           <t>https://lnzweb.com/product-napalm_</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2631,6 +2926,11 @@
           <t>https://lnzweb.com/product-napalm-forte_</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2668,6 +2968,11 @@
           <t>https://lnzweb.com/product-novante</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2705,6 +3010,11 @@
           <t>https://lnzweb.com/product-o-l-dr-ft</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2742,6 +3052,11 @@
           <t>https://lnzweb.com/product-pald-s</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2779,6 +3094,11 @@
           <t>https://lnzweb.com/product-pegas-ke_</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2816,6 +3136,11 @@
           <t>https://lnzweb.com/product-peryn</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2853,6 +3178,11 @@
           <t>https://lnzweb.com/product-p-nogasnik-paiot-yltra</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2890,6 +3220,11 @@
           <t>https://lnzweb.com/product-p-ram-da-lontrel</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2927,6 +3262,11 @@
           <t>https://lnzweb.com/product-presto_</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2964,6 +3304,11 @@
           <t>https://lnzweb.com/product-prostaf</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3001,6 +3346,11 @@
           <t>https://lnzweb.com/product-prosens</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3034,6 +3384,11 @@
           <t>https://lnzweb.com/product-ravak</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3071,6 +3426,11 @@
           <t>https://lnzweb.com/product-radikal-neo</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3108,6 +3468,11 @@
           <t>https://lnzweb.com/product-rim___</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3145,6 +3510,11 @@
           <t>https://lnzweb.com/product-salto-ks_</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3182,6 +3552,11 @@
           <t>https://lnzweb.com/product-sinerid-md_</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3219,6 +3594,11 @@
           <t>https://lnzweb.com/product-s-ltek</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3256,6 +3636,11 @@
           <t>https://lnzweb.com/product-spl-t</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3293,6 +3678,11 @@
           <t>https://lnzweb.com/product-spl-t-dyo-am-star-gold</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3330,6 +3720,11 @@
           <t>https://lnzweb.com/product-stark-ks</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3367,6 +3762,11 @@
           <t>https://lnzweb.com/product-symaro-ks</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3404,6 +3804,11 @@
           <t>https://lnzweb.com/product-tava-rk_</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3441,6 +3846,11 @@
           <t>https://lnzweb.com/product-taler-maks</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3478,6 +3888,11 @@
           <t>https://lnzweb.com/product-taler-ke__</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3515,6 +3930,11 @@
           <t>https://lnzweb.com/product-topal</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3552,6 +3972,11 @@
           <t>https://lnzweb.com/product-yltral-n</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3589,6 +4014,11 @@
           <t>https://lnzweb.com/product-forit</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3626,6 +4056,11 @@
           <t>https://lnzweb.com/product-haryma</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3663,6 +4098,11 @@
           <t>https://lnzweb.com/product-haryma-maks</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3700,6 +4140,11 @@
           <t>https://lnzweb.com/product-hloris-en__</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3737,6 +4182,11 @@
           <t>https://lnzweb.com/product-sherif</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3774,6 +4224,11 @@
           <t>https://lnzweb.com/product-sherif__</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3811,6 +4266,11 @@
           <t>https://lnzweb.com/product-aidaho</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3848,6 +4308,11 @@
           <t>https://lnzweb.com/product-aidaho_</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3885,6 +4350,11 @@
           <t>https://lnzweb.com/product-aidaho__</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3922,6 +4392,11 @@
           <t>https://lnzweb.com/product-at-k-vp_____</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3959,6 +4434,11 @@
           <t>https://lnzweb.com/product-bleid_</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3996,6 +4476,11 @@
           <t>https://lnzweb.com/product-bombardir-akva</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4033,6 +4518,11 @@
           <t>https://lnzweb.com/product-broks-rk__</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4070,6 +4560,11 @@
           <t>https://lnzweb.com/product-ef-mer</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4107,6 +4602,11 @@
           <t>https://lnzweb.com/product-kyshon-ks_</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4144,6 +4644,11 @@
           <t>https://lnzweb.com/product-lat-na-tn</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4181,6 +4686,11 @@
           <t>https://lnzweb.com/product-metaksa_</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4218,6 +4728,11 @@
           <t>https://lnzweb.com/product-mecenat</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4255,6 +4770,11 @@
           <t>https://lnzweb.com/product-mirald-ks___</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4292,6 +4812,11 @@
           <t>https://lnzweb.com/product-napalm___</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4329,6 +4854,11 @@
           <t>https://lnzweb.com/product-napalm__</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4366,6 +4896,11 @@
           <t>https://lnzweb.com/product-pangol-n-vg__</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4403,6 +4938,11 @@
           <t>https://lnzweb.com/product-peryn_</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4440,6 +4980,11 @@
           <t>https://lnzweb.com/product-p-nogasnik-paiot</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4477,6 +5022,11 @@
           <t>https://lnzweb.com/product-presto</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4514,6 +5064,11 @@
           <t>https://lnzweb.com/product-presto__</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4551,6 +5106,11 @@
           <t>https://lnzweb.com/product-sora-net</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4588,6 +5148,11 @@
           <t>https://lnzweb.com/product-sora-net_</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4625,6 +5190,11 @@
           <t>https://lnzweb.com/product-starlent</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4662,6 +5232,11 @@
           <t>https://lnzweb.com/product-taler-ke_</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4697,6 +5272,11 @@
       <c r="G116" t="inlineStr">
         <is>
           <t>https://lnzweb.com/product-tv-ks</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
         </is>
       </c>
     </row>
@@ -4728,6 +5308,11 @@
           <t>https://lnzweb.com/product-tirana</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4757,6 +5342,11 @@
           <t>https://lnzweb.com/product-trinol</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4794,6 +5384,11 @@
           <t>https://lnzweb.com/product-fyks-ya-tn_</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4831,6 +5426,11 @@
           <t>https://lnzweb.com/product-fumigant-56</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4868,6 +5468,11 @@
           <t>https://lnzweb.com/product-haryma_</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4903,6 +5508,11 @@
       <c r="G122" t="inlineStr">
         <is>
           <t>https://lnzweb.com/product-hloris-en_</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:47</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,11 @@
           <t>180.00 грн</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>720.0 грн/кг</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>фольгований пакет 250 г</t>
@@ -1794,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4373,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>442.0 грн/кг</t>
+          <t>4420.0 грн/кг</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4394,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -4982,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-05-26 09:47</t>
+          <t>2026-05-26 13:17</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-05-26 13:17</t>
+          <t>2026-05-26 18:18</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-05-26 18:18</t>
+          <t>2026-05-26 19:34</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-05-26 19:34</t>
+          <t>2026-05-27 18:36</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-05-27 18:36</t>
+          <t>2026-05-28 18:42</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-05-28 18:42</t>
+          <t>2026-05-29 18:24</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-05-29 18:24</t>
+          <t>2026-05-30 12:18</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-05-30 12:18</t>
+          <t>2026-05-31 13:03</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-05-31 13:03</t>
+          <t>2026-06-01 19:22</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-01 19:22</t>
+          <t>2026-06-01 21:46</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-01 21:46</t>
+          <t>2026-06-02 20:22</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-02 20:22</t>
+          <t>2026-06-02 20:48</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-02 20:48</t>
+          <t>2026-06-03 18:05</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-03 18:05</t>
+          <t>2026-06-03 20:40</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-03 20:40</t>
+          <t>2026-06-04 18:00</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-04 18:00</t>
+          <t>2026-06-05 12:56</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-05 12:56</t>
+          <t>2026-06-06 10:33</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-06 10:33</t>
+          <t>2026-06-07 11:17</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-07 11:17</t>
+          <t>2026-06-08 19:50</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-08 19:50</t>
+          <t>2026-06-09 13:48</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-09 13:48</t>
+          <t>2026-06-10 14:42</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-10 14:42</t>
+          <t>2026-06-11 17:09</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-11 17:09</t>
+          <t>2026-06-12 14:22</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-12 14:22</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-13 11:26</t>
+          <t>2026-06-14 11:40</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-14 11:40</t>
+          <t>2026-06-15 19:08</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-15 19:08</t>
+          <t>2026-06-16 18:55</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-16 18:55</t>
+          <t>2026-06-17 14:41</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-17 14:41</t>
+          <t>2026-06-18 14:35</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-18 14:35</t>
+          <t>2026-06-19 14:26</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-19 14:26</t>
+          <t>2026-06-20 11:28</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-20 11:28</t>
+          <t>2026-06-21 08:16</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-21 08:16</t>
+          <t>2026-06-22 09:32</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-22 09:32</t>
+          <t>2026-06-22 16:09</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-22 16:09</t>
+          <t>2026-06-23 07:05</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-23 07:05</t>
+          <t>2026-06-24 07:01</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-24 07:01</t>
+          <t>2026-06-25 07:02</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-25 07:02</t>
+          <t>2026-06-26 07:09</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-26 07:09</t>
+          <t>2026-06-27 06:43</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-27 06:43</t>
+          <t>2026-06-28 07:39</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -461,17 +461,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Абсолют, КС (Дерозал)</t>
+          <t>Бастіон</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1 482.00 грн</t>
+          <t>1 584.00 грн</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>296.4 грн/л</t>
+          <t>316.8 грн/л</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>карбендазим 500г</t>
+          <t>ципроконазол 6,3г</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-absolut-ks</t>
+          <t>https://lnzweb.com/product-bast-on</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Бастіон</t>
+          <t>Диквалан</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1 584.00 грн</t>
+          <t>3 114.00 грн</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>316.8 грн/л</t>
+          <t>155.7 грн/л</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ципроконазол 6,3г</t>
+          <t>дикват 150г</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,39 +533,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-bast-on</t>
+          <t>https://lnzweb.com/product-dikvalan</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Диквалан</t>
+          <t>Дот</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3 114.00 грн</t>
+          <t>3 148.00 грн</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>155.7 грн/л</t>
+          <t>629.6 грн/л</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>дикват 150г</t>
+          <t>ципроконазол 80г</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,12 +575,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-dikvalan</t>
+          <t>https://lnzweb.com/product-dot</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -748,24 +748,24 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Диквалан Макс</t>
+          <t>Напалм Форте, ВК</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5 142.00 грн</t>
+          <t>4 429.00 грн</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>257.1 грн/л</t>
+          <t>221.45 грн/л</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>дикват дибромід 374г</t>
+          <t>калійна сіль гліфосату 550г</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,39 +785,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-dikvalan-maks</t>
+          <t>https://lnzweb.com/product-napalm-forte</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Напалм Форте, ВК</t>
+          <t>Спліт Дуо</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4 429.00 грн</t>
+          <t>3 128.00 грн</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>221.45 грн/л</t>
+          <t>625.6 грн/л</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>калійна сіль гліфосату 550г</t>
+          <t>дифеноконазол 125г</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -827,29 +827,29 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-napalm-forte</t>
+          <t>https://lnzweb.com/product-spl-t-dyo-am-star-gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Парацельс</t>
+          <t>Супер-Мачо</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2 328.00 грн</t>
+          <t>2 515.00 грн</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>465.6 грн/л</t>
+          <t>503.0 грн/л</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>флутріафол 250г</t>
+          <t>модифікований поліефір трісілоксан 85% + аллілоксіполіетиленгліколь  л</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-paracels</t>
+          <t>https://lnzweb.com/product-syper-macho</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Супер-Мачо</t>
+          <t>Фуксія, ТН</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>модифікований поліефір трісілоксан 85% + аллілоксіполіетиленгліколь  л</t>
+          <t>флудіоксоніл 25г</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -911,39 +911,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-syper-macho</t>
+          <t>https://lnzweb.com/product-fyks-ya-tn</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Фуксія, ТН</t>
+          <t>Атік, ВП</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2 515.00 грн</t>
+          <t>180.00 грн</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>503.0 грн/л</t>
+          <t>720.0 грн/кг</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>фольгований пакет 250 г</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>флудіоксоніл 25г</t>
+          <t>ацетаміприд 200г</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -953,39 +953,39 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-fyks-ya-tn</t>
+          <t>https://lnzweb.com/product-at-k-vp_</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Альфа Супер</t>
+          <t>Напалм Супер</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1 469.00 грн</t>
+          <t>5 171.00 грн</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>293.8 грн/л</t>
+          <t>258.55 грн/л</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>альфа-циперметрин 100г</t>
+          <t>калійна сіль гліфосату 663г</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -995,39 +995,39 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-alfa-syper</t>
+          <t>https://lnzweb.com/product-napalm-syper-rayndap-ekstra</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Дот</t>
+          <t>Піногасник Пайот Ультра</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3 148.00 грн</t>
+          <t>671.00 грн</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>629.6 грн/л</t>
+          <t>671.0 грн/л</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>1 л</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ципроконазол 80г</t>
+          <t>модифікований поліефір трісілоксан 50 %</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1037,39 +1037,39 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-dot</t>
+          <t>https://lnzweb.com/product-p-nogasnik-paiot-yltra</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Напалм Супер</t>
+          <t>Сигма</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5 171.00 грн</t>
+          <t>3 082.00 грн</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>258.55 грн/л</t>
+          <t>616.4 грн/л</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>калійна сіль гліфосату 663г</t>
+          <t>азоксистробін 200г</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1079,39 +1079,39 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-napalm-syper-rayndap-ekstra</t>
+          <t>https://lnzweb.com/product-sigma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Піногасник Пайот</t>
+          <t>Атік Макс</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>615.00 грн</t>
+          <t>3 155.00 грн</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>615.0 грн/л</t>
+          <t>631.0 грн/л</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>модифікований поліефір трісілоксан 10-20 % л</t>
+          <t>ацетаміприд 300г</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1121,39 +1121,39 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-paiot</t>
+          <t>https://lnzweb.com/product-at-k-maks</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Альтрон, КС</t>
+          <t>Блейд</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2 141.00 грн</t>
+          <t>3 241.00 грн</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>428.2 грн/л</t>
+          <t>324.1 грн/л</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>10 л</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>альфа-циперметрин 200г</t>
+          <t>клетодим 120г</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1163,39 +1163,39 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-altron-ks</t>
+          <t>https://lnzweb.com/product-bleid</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Літерон</t>
+          <t>Радикал Нео</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7 187.00 грн</t>
+          <t>6 627.00 грн</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>359.35 грн/л</t>
+          <t>1325.4 грн/л</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S-метолахлор 960г</t>
+          <t>азоксистробін 250г</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1205,29 +1205,29 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-l-teron</t>
+          <t>https://lnzweb.com/product-radikal-neo</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Сигма</t>
+          <t>Октант Турбо</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3 082.00 грн</t>
+          <t>3 072.00 грн</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>616.4 грн/л</t>
+          <t>614.4 грн/л</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>азоксистробін 200г</t>
+          <t>тіаметоксам 141г</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1247,39 +1247,39 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sigma</t>
+          <t>https://lnzweb.com/product-oktant-tyrbo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Циркуль, КЕ</t>
+          <t>Палдіс</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1 295.00 грн</t>
+          <t>2 219.00 грн</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>259.0 грн/л</t>
+          <t>2219.0 грн/кг</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>пакет 1 кг</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>лямбда-цигалотрин 50г</t>
+          <t>темботріон 200г</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1289,39 +1289,39 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-cirkyl-ke</t>
+          <t>https://lnzweb.com/product-pald-s</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Сахара</t>
+          <t>Міральд, КС</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5 579.00 грн</t>
+          <t>1 854.00 грн</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>278.95 грн/л</t>
+          <t>370.8 грн/л</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ацетохлор 900г</t>
+          <t>фенпіроксимат 50г</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1331,39 +1331,39 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sahara</t>
+          <t>https://lnzweb.com/product-mirald-ks__</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Октант Турбо</t>
+          <t>Муссон</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3 072.00 грн</t>
+          <t>2 793.00 грн</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>614.4 грн/л</t>
+          <t>279.3 грн/л</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>10 л</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>тіаметоксам 141г</t>
+          <t>нікосульфурон 40г</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1373,39 +1373,39 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-oktant-tyrbo</t>
+          <t>https://lnzweb.com/product-mysson</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Сахара Супер</t>
+          <t>Просенс</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7 439.00 грн</t>
+          <t>1 399.00 грн</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>371.95 грн/л</t>
+          <t>1399.0 грн/кг</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>пакет 1 кг</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ацетохлор 800г</t>
+          <t>емамектин бензоат 100г</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1415,39 +1415,39 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sahara-syper</t>
+          <t>https://lnzweb.com/product-prosens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Твікс</t>
+          <t>Сумаро</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7 369.00 грн</t>
+          <t>4 836.00 грн</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>368.45 грн/л</t>
+          <t>967.2 грн/л</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>хлорпірифос 500г</t>
+          <t>мезотріон 480г</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1457,39 +1457,39 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-tv-ks_</t>
+          <t>https://lnzweb.com/product-symaro-ks</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Шериф Максі</t>
+          <t>Твікс</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1 676.00 грн</t>
+          <t>7 369.00 грн</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3352.0 грн/кг</t>
+          <t>368.45 грн/л</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>трибенурон-метил 563г</t>
+          <t>хлорпірифос 500г</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1499,39 +1499,39 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sherif-maks</t>
+          <t>https://lnzweb.com/product-tv-ks_</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Примус, СЕ</t>
+          <t>Харума Макс</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1 293.00 грн</t>
+          <t>3 911.00 грн</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>258.6 грн/л</t>
+          <t>391.1 грн/л</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>10 л</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2-етилгексиловий ефір 2,4-Д 452г</t>
+          <t>хізалофоп-П-етил 150г</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-primys_</t>
+          <t>https://lnzweb.com/product-haryma-maks</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -1588,34 +1588,34 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Айлар</t>
+          <t>Абсолют, КС (Дерозал)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16 325.00 грн</t>
+          <t>1 482.00 грн</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>816.25 грн/л</t>
+          <t>296.4 грн/л</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>аклоніфен 600г</t>
+          <t>карбендазим 500г</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1625,39 +1625,39 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-ailar-ks</t>
+          <t>https://lnzweb.com/product-absolut-ks</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>АКСАКАЛ</t>
+          <t>Айлар</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1 862.00 грн</t>
+          <t>16 325.00 грн</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3724.0 грн/кг</t>
+          <t>816.25 грн/л</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>флорасулам 250г</t>
+          <t>аклоніфен 600г</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1667,39 +1667,39 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-aksakal____</t>
+          <t>https://lnzweb.com/product-ailar-ks</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Арес, ТН</t>
+          <t>АКСАКАЛ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4 749.00 грн</t>
+          <t>1 862.00 грн</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>949.8 грн/л</t>
+          <t>3724.0 грн/кг</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>металаксил-М 350г</t>
+          <t>флорасулам 250г</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1709,29 +1709,29 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-ares-tn</t>
+          <t>https://lnzweb.com/product-aksakal____</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Атік Макс</t>
+          <t>Альтрон, КС</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3 155.00 грн</t>
+          <t>2 141.00 грн</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>631.0 грн/л</t>
+          <t>428.2 грн/л</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ацетаміприд 300г</t>
+          <t>альфа-циперметрин 200г</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1751,39 +1751,39 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-at-k-maks</t>
+          <t>https://lnzweb.com/product-altron-ks</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Атік, ВП</t>
+          <t>Альфа Супер</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>180.00 грн</t>
+          <t>1 469.00 грн</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>720.0 грн/кг</t>
+          <t>293.8 грн/л</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>фольгований пакет 250 г</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ацетаміприд 200г</t>
+          <t>альфа-циперметрин 100г</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1793,39 +1793,39 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-at-k-vp_</t>
+          <t>https://lnzweb.com/product-alfa-syper</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Атік, ВП</t>
+          <t>Арес, ТН</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>252.00 грн</t>
+          <t>4 749.00 грн</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>504.0 грн/кг</t>
+          <t>949.8 грн/л</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ацетаміприд 200г</t>
+          <t>металаксил-М 350г</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1835,39 +1835,39 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-at-k-vp______</t>
+          <t>https://lnzweb.com/product-ares-tn</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Бантен</t>
+          <t>Атік, ВП</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8 186.00 грн</t>
+          <t>252.00 грн</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>409.3 грн/л</t>
+          <t>504.0 грн/кг</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>бентазон 480г</t>
+          <t>ацетаміприд 200г</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1877,29 +1877,29 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-banten-rk</t>
+          <t>https://lnzweb.com/product-at-k-vp______</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Бетагард</t>
+          <t>Бантен</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9 831.00 грн</t>
+          <t>8 186.00 грн</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>491.55 грн/л</t>
+          <t>409.3 грн/л</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>фенмедифам 91г</t>
+          <t>бентазон 480г</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1919,39 +1919,39 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-betagard</t>
+          <t>https://lnzweb.com/product-banten-rk</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Блейд</t>
+          <t>Бетагард</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3 241.00 грн</t>
+          <t>9 831.00 грн</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>324.1 грн/л</t>
+          <t>491.55 грн/л</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>клетодим 120г</t>
+          <t>фенмедифам 91г</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-bleid</t>
+          <t>https://lnzweb.com/product-betagard</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -2260,34 +2260,34 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ефімер</t>
+          <t>Диквалан Макс</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1 453.00 грн</t>
+          <t>5 142.00 грн</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>290.6 грн/л</t>
+          <t>257.1 грн/л</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2-етилгексиловий ефір 2,4-Д 905г</t>
+          <t>дикват дибромід 374г</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2297,39 +2297,39 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-ef-mer_</t>
+          <t>https://lnzweb.com/product-dikvalan-maks</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Імпреза</t>
+          <t>Ефімер</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10 428.00 грн</t>
+          <t>1 453.00 грн</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>521.4 грн/л</t>
+          <t>290.6 грн/л</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>імазамокс 33г</t>
+          <t>2-етилгексиловий ефір 2,4-Д 905г</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2339,39 +2339,39 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-mpreza</t>
+          <t>https://lnzweb.com/product-ef-mer_</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Кайрос</t>
+          <t>Імпреза</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>31 651.00 грн</t>
+          <t>10 428.00 грн</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>6330.2 грн/л</t>
+          <t>521.4 грн/л</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>флубендіамід 480г</t>
+          <t>імазамокс 33г</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2381,29 +2381,29 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-kairos</t>
+          <t>https://lnzweb.com/product-mpreza</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Камзол Турбо</t>
+          <t>Кайрос</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5 214.00 грн</t>
+          <t>31 651.00 грн</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1042.8 грн/л</t>
+          <t>6330.2 грн/л</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ципроконазол 80г</t>
+          <t>флубендіамід 480г</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2423,29 +2423,29 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-kamzol-tyrbo</t>
+          <t>https://lnzweb.com/product-kairos</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Камзол, РК</t>
+          <t>Камзол Турбо</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4 842.00 грн</t>
+          <t>5 214.00 грн</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>968.4 грн/л</t>
+          <t>1042.8 грн/л</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>метконазол 60г</t>
+          <t>ципроконазол 80г</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2465,39 +2465,39 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-kamzol-rk</t>
+          <t>https://lnzweb.com/product-kamzol-tyrbo</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Кентавр</t>
+          <t>Камзол, РК</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3 352.00 грн</t>
+          <t>4 842.00 грн</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>6704.0 грн/кг</t>
+          <t>968.4 грн/л</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>римсульфурон 500г</t>
+          <t>метконазол 60г</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2507,39 +2507,39 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-kentavr____</t>
+          <t>https://lnzweb.com/product-kamzol-rk</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Клаттер, КЕ</t>
+          <t>Кентавр</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2 328.00 грн</t>
+          <t>3 352.00 грн</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>465.6 грн/л</t>
+          <t>6704.0 грн/кг</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>кломазон 480г</t>
+          <t>римсульфурон 500г</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2549,29 +2549,29 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-klatter-ke</t>
+          <t>https://lnzweb.com/product-kentavr____</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Кушон, КС</t>
+          <t>Клаттер, КЕ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4 831.00 грн</t>
+          <t>2 328.00 грн</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>966.2 грн/л</t>
+          <t>465.6 грн/л</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>метамітрон 700г</t>
+          <t>кломазон 480г</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2591,29 +2591,29 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-kyshon-ks__</t>
+          <t>https://lnzweb.com/product-klatter-ke</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Латіна, ТН</t>
+          <t>Кушон, КС</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6 704.00 грн</t>
+          <t>4 831.00 грн</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1340.8 грн/л</t>
+          <t>966.2 грн/л</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>клотіанідин 600г</t>
+          <t>метамітрон 700г</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2633,29 +2633,29 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-latina-tn</t>
+          <t>https://lnzweb.com/product-kyshon-ks__</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Матар, КС</t>
+          <t>Латіна, ТН</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4 372.00 грн</t>
+          <t>6 704.00 грн</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>874.4 грн/л</t>
+          <t>1340.8 грн/л</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>метрибузин 600г</t>
+          <t>клотіанідин 600г</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-matar-ks</t>
+          <t>https://lnzweb.com/product-latina-tn</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Метакса</t>
+          <t>Літерон</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2 328.00 грн</t>
+          <t>7 187.00 грн</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>465.6 грн/л</t>
+          <t>359.35 грн/л</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>тіаметоксам 350г</t>
+          <t>S-метолахлор 960г</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2717,29 +2717,29 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-metaksa</t>
+          <t>https://lnzweb.com/product-l-teron</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Меценат</t>
+          <t>Матар, КС</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2 328.00 грн</t>
+          <t>4 372.00 грн</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>465.6 грн/л</t>
+          <t>874.4 грн/л</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>пропіконазол 250г</t>
+          <t>метрибузин 600г</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2759,29 +2759,29 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-mecenat_</t>
+          <t>https://lnzweb.com/product-matar-ks</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Міральд, КС</t>
+          <t>Метакса</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1 854.00 грн</t>
+          <t>2 328.00 грн</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>370.8 грн/л</t>
+          <t>465.6 грн/л</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>фенпіроксимат 50г</t>
+          <t>тіаметоксам 350г</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2801,39 +2801,39 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-mirald-ks__</t>
+          <t>https://lnzweb.com/product-metaksa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Муссон</t>
+          <t>Меценат</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2 793.00 грн</t>
+          <t>2 328.00 грн</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>279.3 грн/л</t>
+          <t>465.6 грн/л</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>нікосульфурон 40г</t>
+          <t>пропіконазол 250г</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-mysson</t>
+          <t>https://lnzweb.com/product-mecenat_</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -3016,34 +3016,34 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Палдіс</t>
+          <t>Парацельс</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2 219.00 грн</t>
+          <t>2 328.00 грн</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2219.0 грн/кг</t>
+          <t>465.6 грн/л</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>пакет 1 кг</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>темботріон 200г</t>
+          <t>флутріафол 250г</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-pald-s</t>
+          <t>https://lnzweb.com/product-paracels</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -3142,24 +3142,24 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Піногасник Пайот Ультра</t>
+          <t>Піногасник Пайот</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>671.00 грн</t>
+          <t>615.00 грн</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>671.0 грн/л</t>
+          <t>615.0 грн/л</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>модифікований поліефір трісілоксан 50 %</t>
+          <t>модифікований поліефір трісілоксан 10-20 % л</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3179,12 +3179,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-p-nogasnik-paiot-yltra</t>
+          <t>https://lnzweb.com/product-paiot</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -3268,34 +3268,34 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Просенс</t>
+          <t>Примус, СЕ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1 416.00 грн</t>
+          <t>1 293.00 грн</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2832.0 грн/кг</t>
+          <t>258.6 грн/л</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>емамектин бензоат 100г</t>
+          <t>2-етилгексиловий ефір 2,4-Д 452г</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-prostaf</t>
+          <t>https://lnzweb.com/product-primys_</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -3322,17 +3322,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1 399.00 грн</t>
+          <t>1 416.00 грн</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1399.0 грн/кг</t>
+          <t>2832.0 грн/кг</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>пакет 1 кг</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3347,12 +3347,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-prosens</t>
+          <t>https://lnzweb.com/product-prostaf</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -3390,34 +3390,34 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Радикал Нео</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6 627.00 грн</t>
+          <t>1 676.00 грн</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1325.4 грн/л</t>
+          <t>3352.0 грн/кг</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>азоксистробін 250г</t>
+          <t>римсульфурон 250г</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3427,39 +3427,39 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-radikal-neo</t>
+          <t>https://lnzweb.com/product-rim___</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Сальто, КС</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1 676.00 грн</t>
+          <t>1 843.00 грн</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3352.0 грн/кг</t>
+          <t>368.6 грн/л</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>фольгований пакет 0.5 кг</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>римсульфурон 250г</t>
+          <t>тіофанат-метил 500г</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3469,39 +3469,39 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-rim___</t>
+          <t>https://lnzweb.com/product-salto-ks_</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Сальто, КС</t>
+          <t>Сахара</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1 843.00 грн</t>
+          <t>5 579.00 грн</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>368.6 грн/л</t>
+          <t>278.95 грн/л</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>тіофанат-метил 500г</t>
+          <t>ацетохлор 900г</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3511,39 +3511,39 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-salto-ks_</t>
+          <t>https://lnzweb.com/product-sahara</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Синерид, МД</t>
+          <t>Сахара Супер</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5 208.00 грн</t>
+          <t>7 439.00 грн</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1041.6 грн/л</t>
+          <t>371.95 грн/л</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>20 л</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>тіаклоприд 240г</t>
+          <t>ацетохлор 800г</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3553,29 +3553,29 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-sinerid-md_</t>
+          <t>https://lnzweb.com/product-sahara-syper</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Сілтек</t>
+          <t>Синерид, МД</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2 413.00 грн</t>
+          <t>5 208.00 грн</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>482.6 грн/л</t>
+          <t>1041.6 грн/л</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>суміш клеючих та поверхнево-активних речовин 60% р-н</t>
+          <t>тіаклоприд 240г</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3595,29 +3595,29 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-s-ltek</t>
+          <t>https://lnzweb.com/product-sinerid-md_</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Спліт</t>
+          <t>Сілтек</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3 631.00 грн</t>
+          <t>2 413.00 грн</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>726.2 грн/л</t>
+          <t>482.6 грн/л</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>дифеконазол 250г</t>
+          <t>суміш клеючих та поверхнево-активних речовин 60% р-н</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3637,29 +3637,29 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-spl-t</t>
+          <t>https://lnzweb.com/product-s-ltek</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Спліт Дуо</t>
+          <t>Спліт</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3 128.00 грн</t>
+          <t>3 631.00 грн</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>625.6 грн/л</t>
+          <t>726.2 грн/л</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>дифеноконазол 125г</t>
+          <t>дифеконазол 250г</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-spl-t-dyo-am-star-gold</t>
+          <t>https://lnzweb.com/product-spl-t</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -3726,24 +3726,24 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Сумаро</t>
+          <t>Тава, РК</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>4 836.00 грн</t>
+          <t>1 490.00 грн</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>967.2 грн/л</t>
+          <t>298.0 грн/л</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>мезотріон 480г</t>
+          <t>етефон 480г</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3763,29 +3763,29 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-symaro-ks</t>
+          <t>https://lnzweb.com/product-tava-rk_</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Тава, РК</t>
+          <t>Талер Макс</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1 490.00 грн</t>
+          <t>2 515.00 грн</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>298.0 грн/л</t>
+          <t>503.0 грн/л</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>етефон 480г</t>
+          <t>тебуконазол 500г</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3805,29 +3805,29 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-tava-rk_</t>
+          <t>https://lnzweb.com/product-taler-maks</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Талер Макс</t>
+          <t>Талер, КЕ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2 515.00 грн</t>
+          <t>2 102.00 грн</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>503.0 грн/л</t>
+          <t>420.4 грн/л</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>тебуконазол 500г</t>
+          <t>тебуконазол 250г</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3847,29 +3847,29 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-taler-maks</t>
+          <t>https://lnzweb.com/product-taler-ke__</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Талер, КЕ</t>
+          <t>Топал</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2 102.00 грн</t>
+          <t>5 177.00 грн</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>420.4 грн/л</t>
+          <t>1035.4 грн/л</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>тебуконазол 250г</t>
+          <t>трінексапак-етил 250г</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3889,39 +3889,39 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-taler-ke__</t>
+          <t>https://lnzweb.com/product-topal</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Топал</t>
+          <t>Ультралін</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5 177.00 грн</t>
+          <t>1 282.00 грн</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1035.4 грн/л</t>
+          <t>1282.0 грн/кг</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>1 кг</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>трінексапак-етил 250г</t>
+          <t>цимоксаніл 300г</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3931,39 +3931,39 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-topal</t>
+          <t>https://lnzweb.com/product-yltral-n</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ультралін</t>
+          <t>Форит</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1 282.00 грн</t>
+          <t>2 969.00 грн</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1282.0 грн/кг</t>
+          <t>593.8 грн/л</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1 кг</t>
+          <t>каністра 5 л</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>цимоксаніл 300г</t>
+          <t>флуроксипір 333г</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3973,39 +3973,39 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-yltral-n</t>
+          <t>https://lnzweb.com/product-forit</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Форит</t>
+          <t>Харума</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2 969.00 грн</t>
+          <t>3 537.00 грн</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>593.8 грн/л</t>
+          <t>353.7 грн/л</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>каністра 5 л</t>
+          <t>10 л</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>флуроксипір 333г</t>
+          <t>хізалофоп-П-етил 125г</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4015,39 +4015,39 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-forit</t>
+          <t>https://lnzweb.com/product-haryma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Харума</t>
+          <t>Хлорис, ЕН</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3 537.00 грн</t>
+          <t>1 482.00 грн</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>353.7 грн/л</t>
+          <t>296.4 грн/л</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>хізалофоп-П-етил 125г</t>
+          <t>тебуконазол 15г</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4057,39 +4057,39 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-haryma</t>
+          <t>https://lnzweb.com/product-hloris-en__</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Харума Макс</t>
+          <t>Циркуль, КЕ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3 911.00 грн</t>
+          <t>1 295.00 грн</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>391.1 грн/л</t>
+          <t>259.0 грн/л</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>10 л</t>
+          <t>5 л</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>хізалофоп-П-етил 150г</t>
+          <t>лямбда-цигалотрин 50г</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4099,39 +4099,39 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-haryma-maks</t>
+          <t>https://lnzweb.com/product-cirkyl-ke</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Хлорис, ЕН</t>
+          <t>Шериф Максі</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1 482.00 грн</t>
+          <t>1 676.00 грн</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>296.4 грн/л</t>
+          <t>3352.0 грн/кг</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>5 л</t>
+          <t>фольгований пакет 0.5 кг</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>тебуконазол 15г</t>
+          <t>трибенурон-метил 563г</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://lnzweb.com/product-hloris-en__</t>
+          <t>https://lnzweb.com/product-sherif-maks</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-28 07:39</t>
+          <t>2026-06-29 08:34</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-29 08:34</t>
+          <t>2026-06-30 07:09</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-30 07:09</t>
+          <t>2026-07-01 07:56</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-01 07:56</t>
+          <t>2026-07-02 06:56</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-02 06:56</t>
+          <t>2026-07-03 06:50</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50</t>
+          <t>2026-07-04 06:36</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-04 06:36</t>
+          <t>2026-07-05 06:56</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-05 06:56</t>
+          <t>2026-07-06 08:05</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-06 08:05</t>
+          <t>2026-07-07 07:02</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-07 07:02</t>
+          <t>2026-07-08 06:14</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-08 06:14</t>
+          <t>2026-07-09 07:04</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-09 07:04</t>
+          <t>2026-07-10 07:02</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-10 07:02</t>
+          <t>2026-07-11 05:59</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-11 05:59</t>
+          <t>2026-07-12 06:19</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-12 06:19</t>
+          <t>2026-07-13 06:39</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-13 06:39</t>
+          <t>2026-07-14 05:54</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-14 05:54</t>
+          <t>2026-07-15 05:56</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-15 05:56</t>
+          <t>2026-07-16 06:01</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-16 06:01</t>
+          <t>2026-07-17 06:01</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-17 06:01</t>
+          <t>2026-07-18 05:50</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-18 05:50</t>
+          <t>2026-07-19 06:14</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-19 06:14</t>
+          <t>2026-07-20 06:35</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-20 06:35</t>
+          <t>2026-07-21 06:14</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-21 06:14</t>
+          <t>2026-07-22 06:12</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-22 06:12</t>
+          <t>2026-07-23 06:17</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-23 06:17</t>
+          <t>2026-07-24 06:11</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-24 06:11</t>
+          <t>2026-07-25 06:03</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-25 06:03</t>
+          <t>2026-07-26 06:22</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-26 06:22</t>
+          <t>2026-07-27 06:50</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-27 06:50</t>
+          <t>2026-07-28 06:11</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-28 06:11</t>
+          <t>2026-07-29 06:16</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-29 06:16</t>
+          <t>2026-07-30 06:09</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-30 06:09</t>
+          <t>2026-07-31 06:32</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-31 06:32</t>
+          <t>2026-08-01 06:17</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-08-01 06:17</t>
+          <t>2026-08-02 06:19</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-08-02 06:19</t>
+          <t>2026-08-03 06:50</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-08-03 06:50</t>
+          <t>2026-08-04 06:13</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-08-04 06:13</t>
+          <t>2026-08-05 06:09</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-08-05 06:09</t>
+          <t>2026-08-06 06:13</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-08-06 06:13</t>
+          <t>2026-08-07 05:18</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-08-07 05:18</t>
+          <t>2026-08-08 04:36</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-08-08 04:36</t>
+          <t>2026-08-09 04:48</t>
         </is>
       </c>
     </row>

--- a/lnz_defenda.xlsx
+++ b/lnz_defenda.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 05:08</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-09 04:48</t>
+          <t>2026-08-10 